--- a/Excel_PowerBI/data_analysis_excel.xlsx
+++ b/Excel_PowerBI/data_analysis_excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\新建文件夹\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D01F59-367F-4358-A23C-7F8B37B3D0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF987BD-7148-4217-8972-BB8DABE9445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" tabRatio="822" activeTab="1" xr2:uid="{FDB7D11C-BD31-4433-8A29-7E2A7F13989A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" tabRatio="822" firstSheet="1" activeTab="9" xr2:uid="{FDB7D11C-BD31-4433-8A29-7E2A7F13989A}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel常用功能" sheetId="13" r:id="rId1"/>
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="848">
   <si>
     <t>TRIM</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3456,13 +3456,126 @@
     <t>旭日图（圆环图）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算两个日期之间相隔的天数、月数或年数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATEDIF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATEDIF(start_date,end_date,unit)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_date 必需 开始日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>end_date 必需 结束日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit 要返回的信息类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Y”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一段时期内的整年数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“M”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一段时期内的整月数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“D”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一段时期内的天数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“MD”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_date 与 end_date 之间天数之差。 忽略日期中的月份和年份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“YM”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_date 与 end_date 之间月份之差。 忽略日期中的天和年份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“YD”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_date 与 end_date 的日期部分之差。 忽略日期中的年份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>end_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -3704,7 +3817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3870,17 +3983,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3889,9 +3999,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3909,20 +4016,47 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4439,7 +4573,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[数据分析（使用Excel）.xlsx]Excel常用功能!数据透视表1</c:name>
+    <c:name>[data_analysis_excel.xlsx]Excel常用功能!数据透视表1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -5530,7 +5664,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[数据分析（使用Excel）.xlsx]Excel常用功能!数据透视表4</c:name>
+    <c:name>[data_analysis_excel.xlsx]Excel常用功能!数据透视表4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -6373,7 +6507,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[数据分析（使用Excel）.xlsx]表格+数据透视+切片器!数据透视表5</c:name>
+    <c:name>[data_analysis_excel.xlsx]表格+数据透视+切片器!数据透视表5</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -15297,7 +15431,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98CDF090-F36B-4C7A-AE69-CA5D4E90BB5A}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.59765625" customWidth="1"/>
@@ -15356,7 +15490,7 @@
       <c r="D3" s="12"/>
       <c r="E3" s="36">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="F3" t="s">
         <v>331</v>
@@ -15378,7 +15512,7 @@
       <c r="A5" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="56" t="s">
         <v>332</v>
       </c>
       <c r="C5" s="11" t="s">
@@ -15397,12 +15531,12 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="12"/>
-      <c r="B6" s="56"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="37">
         <f ca="1">NOW()</f>
-        <v>46030.615715972221</v>
+        <v>46102.60768854167</v>
       </c>
       <c r="F6" t="s">
         <v>335</v>
@@ -15424,7 +15558,7 @@
       <c r="A8" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="56" t="s">
         <v>337</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -15449,7 +15583,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="12"/>
-      <c r="B9" s="56"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="s">
         <v>339</v>
@@ -15494,13 +15628,13 @@
       <c r="A12" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="56" t="s">
         <v>345</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="56" t="s">
         <v>346</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -15515,16 +15649,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="12"/>
-      <c r="B13" s="56"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="56"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="17">
         <f ca="1">YEAR(F13)</f>
         <v>2026</v>
       </c>
       <c r="F13" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="I13" s="7"/>
     </row>
@@ -15539,7 +15673,7 @@
       </c>
       <c r="F14" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="G14">
         <v>1982</v>
@@ -15561,13 +15695,13 @@
       <c r="A16" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="56" t="s">
         <v>348</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="56" t="s">
         <v>346</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -15582,16 +15716,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
-      <c r="B17" s="56"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="56"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="17">
         <f ca="1">MONTH(F17)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -15610,13 +15744,13 @@
       <c r="A19" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="56" t="s">
         <v>352</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="56" t="s">
         <v>346</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -15631,16 +15765,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="12"/>
-      <c r="B20" s="56"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="56"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="17">
         <f ca="1">DAY(F20)</f>
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F20" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="I20" s="7"/>
     </row>
@@ -15659,13 +15793,13 @@
       <c r="A22" s="30" t="s">
         <v>689</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="56" t="s">
         <v>690</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="56" t="s">
         <v>692</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -15682,9 +15816,9 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="12"/>
-      <c r="B23" s="56"/>
+      <c r="B23" s="55"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="56"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="17">
         <f>_xlfn.DAYS(F23,G23)</f>
         <v>364</v>
@@ -15701,7 +15835,7 @@
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="56"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="17">
         <f>F23-G23</f>
         <v>364</v>
@@ -15723,7 +15857,7 @@
       <c r="A26" s="30" t="s">
         <v>705</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="56" t="s">
         <v>706</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -15742,19 +15876,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="12"/>
-      <c r="B27" s="56"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="12"/>
       <c r="D27" s="7"/>
       <c r="E27" s="17">
         <f ca="1">WEEKDAY(G27)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>711</v>
       </c>
       <c r="G27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="I27" s="52"/>
     </row>
@@ -15765,14 +15899,14 @@
       <c r="D28" s="7"/>
       <c r="E28" s="17">
         <f ca="1">WEEKDAY(G28,I28)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>711</v>
       </c>
       <c r="G28" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="H28" t="s">
         <v>708</v>
@@ -15944,22 +16078,271 @@
       <c r="H41" s="9"/>
       <c r="I41" s="10"/>
     </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A42" s="30" t="s">
+        <v>822</v>
+      </c>
+      <c r="B42" s="56" t="s">
+        <v>821</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>823</v>
+      </c>
+      <c r="D42" s="74" t="s">
+        <v>824</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A43" s="12"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="17">
+        <f>DATEDIF(F43,G43,H43)</f>
+        <v>1</v>
+      </c>
+      <c r="F43" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G43" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H43" s="78" t="s">
+        <v>831</v>
+      </c>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="60" t="s">
+        <v>825</v>
+      </c>
+      <c r="E44" s="17">
+        <f t="shared" ref="E44:E48" si="0">DATEDIF(F44,G44,H44)</f>
+        <v>14</v>
+      </c>
+      <c r="F44" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G44" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H44" s="78" t="s">
+        <v>820</v>
+      </c>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A45" s="12"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="17">
+        <f t="shared" si="0"/>
+        <v>449</v>
+      </c>
+      <c r="F45" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G45" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H45" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A46" s="12"/>
+      <c r="B46" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="C46" s="75" t="s">
+        <v>828</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="E46" s="17">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="F46" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G46" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H46" s="78" t="s">
+        <v>838</v>
+      </c>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A47" s="12"/>
+      <c r="B47" s="76" t="s">
+        <v>829</v>
+      </c>
+      <c r="C47" s="75" t="s">
+        <v>830</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F47" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G47" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H47" s="78" t="s">
+        <v>841</v>
+      </c>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A48" s="12"/>
+      <c r="B48" s="76" t="s">
+        <v>832</v>
+      </c>
+      <c r="C48" s="75" t="s">
+        <v>833</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="17">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="F48" s="77">
+        <v>45327</v>
+      </c>
+      <c r="G48" s="77">
+        <v>45776</v>
+      </c>
+      <c r="H48" s="79" t="s">
+        <v>844</v>
+      </c>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A49" s="12"/>
+      <c r="B49" s="76" t="s">
+        <v>834</v>
+      </c>
+      <c r="C49" s="75" t="s">
+        <v>835</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="75"/>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A50" s="12"/>
+      <c r="B50" s="76" t="s">
+        <v>836</v>
+      </c>
+      <c r="C50" s="75" t="s">
+        <v>837</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A51" s="12"/>
+      <c r="B51" s="76" t="s">
+        <v>839</v>
+      </c>
+      <c r="C51" s="75" t="s">
+        <v>840</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="75"/>
+      <c r="G51" s="75"/>
+      <c r="H51" s="75"/>
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A52" s="12"/>
+      <c r="B52" s="76" t="s">
+        <v>842</v>
+      </c>
+      <c r="C52" s="75" t="s">
+        <v>843</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A53" s="12"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A54" s="13"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16000,13 +16383,13 @@
       <c r="A2" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>354</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>355</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -16023,9 +16406,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="56"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="17">
         <f>ROUND(F3,G3)</f>
         <v>3.1415999999999999</v>
@@ -16050,13 +16433,13 @@
       <c r="A5" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="55" t="s">
         <v>357</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="55" t="s">
         <v>355</v>
       </c>
       <c r="E5" s="17">
@@ -16073,9 +16456,9 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="12"/>
-      <c r="B6" s="56"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="12"/>
-      <c r="D6" s="56"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="6"/>
       <c r="I6" s="7"/>
     </row>
@@ -16091,13 +16474,13 @@
       <c r="A8" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="55" t="s">
         <v>358</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="D8" s="56" t="s">
+      <c r="D8" s="55" t="s">
         <v>355</v>
       </c>
       <c r="E8" s="17">
@@ -16114,9 +16497,9 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="12"/>
-      <c r="B9" s="56"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="56"/>
+      <c r="D9" s="55"/>
       <c r="E9" s="6"/>
       <c r="I9" s="7"/>
     </row>
@@ -16141,7 +16524,7 @@
       <c r="C11" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="56" t="s">
         <v>363</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -16158,7 +16541,7 @@
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="56"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="17">
         <f>ABS(F12)</f>
         <v>3.14</v>
@@ -16211,7 +16594,7 @@
       <c r="A16" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="56" t="s">
         <v>365</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -16234,7 +16617,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
-      <c r="B17" s="56"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
         <v>367</v>
@@ -16266,7 +16649,7 @@
       <c r="A19" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="56" t="s">
         <v>369</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -16285,18 +16668,18 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="12"/>
-      <c r="B20" s="56"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="E20" s="17">
         <f ca="1">RAND()</f>
-        <v>0.50017801536052375</v>
+        <v>0.14395815309265092</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="12"/>
-      <c r="B21" s="56"/>
+      <c r="B21" s="55"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="6"/>
@@ -16317,7 +16700,7 @@
       <c r="A23" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="56" t="s">
         <v>372</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -16340,14 +16723,14 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="12"/>
-      <c r="B24" s="56"/>
+      <c r="B24" s="55"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
         <v>374</v>
       </c>
       <c r="E24" s="17">
         <f ca="1">RANDBETWEEN(F24,G24)</f>
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -16423,13 +16806,13 @@
       <c r="A2" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>423</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>427</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -16448,9 +16831,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="56"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="6" t="s">
         <v>394</v>
       </c>
@@ -16470,10 +16853,10 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="58" t="s">
         <v>429</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="60" t="s">
         <v>428</v>
       </c>
       <c r="E4" s="17" t="str" cm="1">
@@ -16496,8 +16879,8 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="61"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="60"/>
       <c r="E5" s="6" t="str">
         <v>Row 6</v>
       </c>
@@ -16529,13 +16912,13 @@
       <c r="A7" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="56" t="s">
         <v>430</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="56" t="s">
         <v>435</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -16552,9 +16935,9 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="12"/>
-      <c r="B8" s="56"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="56"/>
+      <c r="D8" s="55"/>
       <c r="E8">
         <v>2</v>
       </c>
@@ -16570,7 +16953,7 @@
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="56"/>
+      <c r="D9" s="55"/>
       <c r="E9" t="s">
         <v>394</v>
       </c>
@@ -16591,7 +16974,7 @@
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="55" t="s">
         <v>436</v>
       </c>
       <c r="E10" s="19" t="str" cm="1">
@@ -16615,7 +16998,7 @@
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="56"/>
+      <c r="D11" s="55"/>
       <c r="E11" t="str">
         <v>Row 6</v>
       </c>
@@ -16636,7 +17019,7 @@
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="56"/>
+      <c r="D12" s="55"/>
       <c r="E12" t="str">
         <v>Row 2</v>
       </c>
@@ -16657,7 +17040,7 @@
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="55" t="s">
         <v>437</v>
       </c>
       <c r="E13" t="str">
@@ -16680,7 +17063,7 @@
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
-      <c r="D14" s="56"/>
+      <c r="D14" s="55"/>
       <c r="E14" t="str">
         <v>Row 4</v>
       </c>
@@ -16701,7 +17084,7 @@
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="56"/>
+      <c r="D15" s="55"/>
       <c r="E15" t="str">
         <v>Row 5</v>
       </c>
@@ -16817,13 +17200,13 @@
       <c r="A21" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="56" t="s">
         <v>439</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="56" t="s">
         <v>438</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="56" t="s">
         <v>442</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -16838,9 +17221,9 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="12"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
       <c r="E22">
         <v>1</v>
       </c>
@@ -16851,9 +17234,9 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="12"/>
-      <c r="B23" s="56"/>
+      <c r="B23" s="55"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="56" t="s">
+      <c r="D23" s="55" t="s">
         <v>443</v>
       </c>
       <c r="E23" t="s">
@@ -16876,7 +17259,7 @@
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="56"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="19" t="str" cm="1">
         <f t="array" ref="E24:I33">_xlfn.SORTBY(A115:E124,B115:B124,E22,F115:F124,F22)</f>
         <v>Row 6</v>
@@ -16898,7 +17281,7 @@
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="56" t="s">
+      <c r="D25" s="55" t="s">
         <v>444</v>
       </c>
       <c r="E25" t="str">
@@ -16921,7 +17304,7 @@
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="56"/>
+      <c r="D26" s="55"/>
       <c r="E26" t="str">
         <v>Row 3</v>
       </c>
@@ -16942,7 +17325,7 @@
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="56"/>
+      <c r="D27" s="55"/>
       <c r="E27" t="str">
         <v>Row 2</v>
       </c>
@@ -17100,13 +17483,13 @@
       <c r="A35" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="56" t="s">
         <v>445</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="56" t="s">
         <v>448</v>
       </c>
       <c r="E35" s="4" t="s">
@@ -17125,9 +17508,9 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="12"/>
-      <c r="B36" s="56"/>
+      <c r="B36" s="55"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="56"/>
+      <c r="D36" s="55"/>
       <c r="E36" t="s">
         <v>395</v>
       </c>
@@ -17143,7 +17526,7 @@
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="56"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="19" t="str" cm="1">
         <f t="array" ref="E37:E43">_xlfn.UNIQUE(B115:B124,F35,H35)</f>
         <v>A</v>
@@ -17161,7 +17544,7 @@
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
-      <c r="D38" s="56"/>
+      <c r="D38" s="55"/>
       <c r="E38" t="str">
         <v>B</v>
       </c>
@@ -17177,7 +17560,7 @@
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="56"/>
+      <c r="D39" s="55"/>
       <c r="E39" t="str">
         <v>C</v>
       </c>
@@ -17193,7 +17576,7 @@
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="56" t="s">
+      <c r="D40" s="55" t="s">
         <v>449</v>
       </c>
       <c r="E40" t="str">
@@ -17211,7 +17594,7 @@
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="56"/>
+      <c r="D41" s="55"/>
       <c r="E41" t="str">
         <v>E</v>
       </c>
@@ -17227,7 +17610,7 @@
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="56"/>
+      <c r="D42" s="55"/>
       <c r="E42" t="str">
         <v>F</v>
       </c>
@@ -17243,7 +17626,7 @@
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
-      <c r="D43" s="56"/>
+      <c r="D43" s="55"/>
       <c r="E43" t="str">
         <v>G</v>
       </c>
@@ -17259,7 +17642,7 @@
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
-      <c r="D44" s="56"/>
+      <c r="D44" s="55"/>
       <c r="G44" t="str">
         <v>F</v>
       </c>
@@ -17272,7 +17655,7 @@
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="56"/>
+      <c r="D45" s="55"/>
       <c r="G45" t="str">
         <v>G</v>
       </c>
@@ -17296,7 +17679,7 @@
       <c r="A47" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="56" t="s">
         <v>459</v>
       </c>
       <c r="C47" s="11" t="s">
@@ -17321,9 +17704,9 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="12"/>
-      <c r="B48" s="56"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="12"/>
-      <c r="D48" s="56" t="s">
+      <c r="D48" s="55" t="s">
         <v>452</v>
       </c>
       <c r="E48" s="6" t="s">
@@ -17344,7 +17727,7 @@
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
-      <c r="D49" s="56"/>
+      <c r="D49" s="55"/>
       <c r="E49" s="17" cm="1">
         <f t="array" ref="E49:I53">_xlfn.SEQUENCE(F47,H47,F48,H48)</f>
         <v>1</v>
@@ -17366,7 +17749,7 @@
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
-      <c r="D50" s="56" t="s">
+      <c r="D50" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E50" s="6">
@@ -17389,7 +17772,7 @@
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
-      <c r="D51" s="56"/>
+      <c r="D51" s="55"/>
       <c r="E51" s="6">
         <v>21</v>
       </c>
@@ -17410,7 +17793,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
-      <c r="D52" s="56" t="s">
+      <c r="D52" s="55" t="s">
         <v>454</v>
       </c>
       <c r="E52" s="6">
@@ -17433,7 +17816,7 @@
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
-      <c r="D53" s="56"/>
+      <c r="D53" s="55"/>
       <c r="E53" s="6">
         <v>41</v>
       </c>
@@ -17468,10 +17851,10 @@
       <c r="B55" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="C55" s="56" t="s">
         <v>460</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="56" t="s">
         <v>467</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -17493,8 +17876,8 @@
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
       <c r="E56" s="6">
         <v>5</v>
       </c>
@@ -17515,54 +17898,54 @@
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="13"/>
-      <c r="D57" s="61" t="s">
+      <c r="D57" s="60" t="s">
         <v>452</v>
       </c>
       <c r="E57" s="17" cm="1">
         <f t="array" aca="1" ref="E57:I61" ca="1">_xlfn.RANDARRAY(E56,F56,G56,H56,I56)</f>
-        <v>75.478090826152155</v>
+        <v>51.532479003880184</v>
       </c>
       <c r="F57">
         <f ca="1"/>
-        <v>85.095490020564014</v>
+        <v>73.970632157640992</v>
       </c>
       <c r="G57">
         <f ca="1"/>
-        <v>54.045991252370158</v>
+        <v>13.018512767170833</v>
       </c>
       <c r="H57">
         <f ca="1"/>
-        <v>43.507609555284702</v>
+        <v>84.682815450767933</v>
       </c>
       <c r="I57" s="7">
         <f ca="1"/>
-        <v>8.0536411312646976</v>
+        <v>90.924206535762906</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="61"/>
+      <c r="D58" s="60"/>
       <c r="E58" s="6">
         <f ca="1"/>
-        <v>42.878407279272139</v>
+        <v>38.255387135334672</v>
       </c>
       <c r="F58">
         <f ca="1"/>
-        <v>70.574854276410036</v>
+        <v>10.450609693076132</v>
       </c>
       <c r="G58">
         <f ca="1"/>
-        <v>62.28142244000945</v>
+        <v>34.058515095414663</v>
       </c>
       <c r="H58">
         <f ca="1"/>
-        <v>41.12406711839968</v>
+        <v>49.204779405452982</v>
       </c>
       <c r="I58" s="7">
         <f ca="1"/>
-        <v>70.164456343261676</v>
+        <v>55.44803359779533</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
@@ -17571,54 +17954,54 @@
       <c r="C59" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="D59" s="61" t="s">
+      <c r="D59" s="60" t="s">
         <v>468</v>
       </c>
       <c r="E59" s="6">
         <f ca="1"/>
-        <v>65.611624233801976</v>
+        <v>62.788438346455564</v>
       </c>
       <c r="F59">
         <f ca="1"/>
-        <v>41.651359435195729</v>
+        <v>64.188140701317124</v>
       </c>
       <c r="G59">
         <f ca="1"/>
-        <v>33.016311898773424</v>
+        <v>50.159004283691232</v>
       </c>
       <c r="H59">
         <f ca="1"/>
-        <v>74.555073325112915</v>
+        <v>87.941821059238777</v>
       </c>
       <c r="I59" s="7">
         <f ca="1"/>
-        <v>52.156962846314457</v>
+        <v>80.215594153494337</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="61"/>
+      <c r="D60" s="60"/>
       <c r="E60" s="6">
         <f ca="1"/>
-        <v>27.236520519790318</v>
+        <v>57.274252088469268</v>
       </c>
       <c r="F60">
         <f ca="1"/>
-        <v>58.686342875607309</v>
+        <v>33.592647434550969</v>
       </c>
       <c r="G60">
         <f ca="1"/>
-        <v>52.042082178454052</v>
+        <v>84.659714001041934</v>
       </c>
       <c r="H60">
         <f ca="1"/>
-        <v>94.615317822928873</v>
+        <v>45.006139944061545</v>
       </c>
       <c r="I60" s="7">
         <f ca="1"/>
-        <v>79.676389301980663</v>
+        <v>40.316756404084146</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
@@ -17630,23 +18013,23 @@
       <c r="D61" s="7"/>
       <c r="E61" s="6">
         <f ca="1"/>
-        <v>79.03723107037581</v>
+        <v>57.547578446248892</v>
       </c>
       <c r="F61">
         <f ca="1"/>
-        <v>42.9588136057654</v>
+        <v>90.568417162446181</v>
       </c>
       <c r="G61">
         <f ca="1"/>
-        <v>18.427952587536822</v>
+        <v>58.667145247641116</v>
       </c>
       <c r="H61">
         <f ca="1"/>
-        <v>6.950869822666931</v>
+        <v>24.815261958652798</v>
       </c>
       <c r="I61" s="7">
         <f ca="1"/>
-        <v>86.706467002112561</v>
+        <v>19.027843259440971</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
@@ -17664,32 +18047,32 @@
       <c r="A63" s="30" t="s">
         <v>471</v>
       </c>
-      <c r="B63" s="55" t="s">
+      <c r="B63" s="56" t="s">
         <v>485</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="C63" s="56" t="s">
         <v>472</v>
       </c>
-      <c r="D63" s="55" t="s">
+      <c r="D63" s="56" t="s">
         <v>478</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F63" s="57" t="s">
+      <c r="F63" s="66" t="s">
         <v>477</v>
       </c>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="58"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="66"/>
+      <c r="I63" s="67"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="B64" s="56"/>
-      <c r="C64" s="62"/>
-      <c r="D64" s="56"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="55"/>
       <c r="E64" s="6" t="s">
         <v>473</v>
       </c>
@@ -17727,10 +18110,10 @@
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
-      <c r="C66" s="59" t="s">
+      <c r="C66" s="58" t="s">
         <v>481</v>
       </c>
-      <c r="D66" s="61" t="s">
+      <c r="D66" s="60" t="s">
         <v>479</v>
       </c>
       <c r="E66" s="17" t="str" cm="1">
@@ -17753,18 +18136,18 @@
     <row r="67" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
-      <c r="C67" s="59"/>
-      <c r="D67" s="61"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="60"/>
       <c r="E67" s="6"/>
       <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
-      <c r="C68" s="59" t="s">
+      <c r="C68" s="58" t="s">
         <v>482</v>
       </c>
-      <c r="D68" s="61" t="s">
+      <c r="D68" s="60" t="s">
         <v>480</v>
       </c>
       <c r="E68" s="17" t="str" cm="1">
@@ -17785,8 +18168,8 @@
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
-      <c r="C69" s="59"/>
-      <c r="D69" s="61"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="60"/>
       <c r="E69" s="6" t="str">
         <v>执行。</v>
       </c>
@@ -17807,7 +18190,7 @@
       <c r="C70" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="D70" s="61"/>
+      <c r="D70" s="60"/>
       <c r="E70" s="6" t="s">
         <v>484</v>
       </c>
@@ -17828,7 +18211,7 @@
       <c r="A72" s="30" t="s">
         <v>772</v>
       </c>
-      <c r="B72" s="55" t="s">
+      <c r="B72" s="56" t="s">
         <v>771</v>
       </c>
       <c r="C72" s="11" t="s">
@@ -17851,9 +18234,9 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A73" s="12"/>
-      <c r="B73" s="56"/>
+      <c r="B73" s="55"/>
       <c r="C73" s="12"/>
-      <c r="D73" s="56" t="s">
+      <c r="D73" s="55" t="s">
         <v>775</v>
       </c>
       <c r="E73" s="17" cm="1">
@@ -17876,9 +18259,9 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A74" s="12"/>
-      <c r="B74" s="56"/>
+      <c r="B74" s="55"/>
       <c r="C74" s="12"/>
-      <c r="D74" s="56"/>
+      <c r="D74" s="55"/>
       <c r="E74" s="17">
         <f ca="1"/>
         <v>3</v>
@@ -17901,7 +18284,7 @@
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
-      <c r="D75" s="56"/>
+      <c r="D75" s="55"/>
       <c r="E75" s="17">
         <f ca="1"/>
         <v>4</v>
@@ -17976,10 +18359,10 @@
       <c r="A80" s="30" t="s">
         <v>488</v>
       </c>
-      <c r="B80" s="55" t="s">
+      <c r="B80" s="56" t="s">
         <v>489</v>
       </c>
-      <c r="C80" s="55" t="s">
+      <c r="C80" s="56" t="s">
         <v>487</v>
       </c>
       <c r="D80" s="4"/>
@@ -18001,8 +18384,8 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A81" s="12"/>
-      <c r="B81" s="56"/>
-      <c r="C81" s="56"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="55"/>
       <c r="E81" s="6">
         <v>1</v>
       </c>
@@ -18021,8 +18404,8 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A82" s="12"/>
-      <c r="B82" s="56"/>
-      <c r="C82" s="56"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="55"/>
       <c r="E82" s="17" t="str" cm="1">
         <f t="array" ref="E82:I90">_xlfn.PIVOTBY(B114:B124,C114:C124,E114:E124,_xleta.SUM,E81,F81,G81,H81,I81)</f>
         <v/>
@@ -18043,7 +18426,7 @@
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
-      <c r="C83" s="56"/>
+      <c r="C83" s="55"/>
       <c r="E83" s="6" t="str">
         <v>A</v>
       </c>
@@ -18209,21 +18592,21 @@
       <c r="I93" s="7"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A94" s="59" t="s">
+      <c r="A94" s="58" t="s">
         <v>499</v>
       </c>
-      <c r="B94" s="60"/>
-      <c r="C94" s="60"/>
-      <c r="D94" s="60"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
       <c r="I94" s="7"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A95" s="59" t="s">
+      <c r="A95" s="58" t="s">
         <v>501</v>
       </c>
-      <c r="B95" s="60"/>
-      <c r="C95" s="60"/>
-      <c r="D95" s="60"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
       <c r="I95" s="7"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
@@ -18643,6 +19026,33 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="D35:D39"/>
+    <mergeCell ref="D40:D45"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="D63:D64"/>
     <mergeCell ref="B63:B64"/>
     <mergeCell ref="C80:C83"/>
     <mergeCell ref="B80:B82"/>
@@ -18654,33 +19064,6 @@
     <mergeCell ref="D66:D67"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="D73:D75"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="D35:D39"/>
-    <mergeCell ref="D40:D45"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20845,13 +21228,13 @@
       <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="55" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -20864,9 +21247,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="15"/>
-      <c r="D3" s="56"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="17" t="str">
         <f>TRIM(F3)</f>
         <v>abcd efg</v>
@@ -20878,7 +21261,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="56"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="15"/>
       <c r="D4" s="12"/>
       <c r="E4" s="17" t="str">
@@ -20901,13 +21284,13 @@
       <c r="A6" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="56" t="s">
         <v>377</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="56" t="s">
         <v>382</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -20922,9 +21305,9 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="12"/>
-      <c r="B7" s="56"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="56"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="17">
         <f>LEN(F7)</f>
         <v>8</v>
@@ -20952,13 +21335,13 @@
       <c r="A9" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="55" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="55" t="s">
         <v>23</v>
       </c>
       <c r="E9" t="s">
@@ -20974,9 +21357,9 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="12"/>
-      <c r="B10" s="56"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="56"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="19" t="str">
         <f>LEFT(F10)</f>
         <v>a</v>
@@ -20988,9 +21371,9 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="12"/>
-      <c r="B11" s="56"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="56" t="s">
+      <c r="D11" s="55" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="19" t="str">
@@ -21006,7 +21389,7 @@
       <c r="A12" s="12"/>
       <c r="B12" s="15"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="56"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="19" t="str">
         <f t="shared" ref="E12:E15" si="0">LEFT(F12,G12)</f>
         <v>abcd</v>
@@ -21023,7 +21406,7 @@
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="56"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="19" t="str">
         <f t="shared" si="0"/>
         <v>你好</v>
@@ -21040,7 +21423,7 @@
       <c r="A14" s="12"/>
       <c r="B14" s="15"/>
       <c r="C14" s="12"/>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="55" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="19" t="str">
@@ -21059,7 +21442,7 @@
       <c r="A15" s="12"/>
       <c r="B15" s="15"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="56"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="19" t="str">
         <f t="shared" si="0"/>
         <v>你好世界</v>
@@ -21087,7 +21470,7 @@
       <c r="A17" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -21110,7 +21493,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="12"/>
-      <c r="B18" s="56"/>
+      <c r="B18" s="55"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="19" t="str">
@@ -21124,7 +21507,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="12"/>
-      <c r="B19" s="56"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="19" t="str">
@@ -21219,13 +21602,13 @@
       <c r="A25" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="56" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="56" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -21244,9 +21627,9 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="12"/>
-      <c r="B26" s="56"/>
+      <c r="B26" s="55"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="56"/>
+      <c r="D26" s="55"/>
       <c r="E26" s="17" t="str">
         <f>MID(F26,G26,H26)</f>
         <v>cdef</v>
@@ -21264,9 +21647,9 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="12"/>
-      <c r="B27" s="56"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="55" t="s">
         <v>33</v>
       </c>
       <c r="E27" s="17" t="str">
@@ -21286,9 +21669,9 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="12"/>
-      <c r="B28" s="56"/>
+      <c r="B28" s="55"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="56"/>
+      <c r="D28" s="55"/>
       <c r="E28" s="17" t="str">
         <f t="shared" ref="E28:E31" si="3">MID(F28,G28,H28)</f>
         <v/>
@@ -21308,7 +21691,7 @@
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="56"/>
+      <c r="D29" s="55"/>
       <c r="E29" s="17" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -21328,7 +21711,7 @@
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="55" t="s">
         <v>36</v>
       </c>
       <c r="E30" s="17" t="str">
@@ -21350,7 +21733,7 @@
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
-      <c r="D31" s="56"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="17" t="str">
         <f t="shared" si="3"/>
         <v>好世界</v>
@@ -21370,7 +21753,7 @@
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
-      <c r="D32" s="62"/>
+      <c r="D32" s="57"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
@@ -21381,13 +21764,13 @@
       <c r="A33" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="56" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="55" t="s">
+      <c r="D33" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -21404,9 +21787,9 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="56"/>
+      <c r="B34" s="55"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="56"/>
+      <c r="D34" s="55"/>
       <c r="E34" s="17" t="str">
         <f>TEXT(F34,G34)</f>
         <v>$1,234.57</v>
@@ -21421,18 +21804,18 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="12"/>
-      <c r="B35" s="56"/>
+      <c r="B35" s="55"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="56" t="s">
+      <c r="D35" s="55" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="17" t="str">
         <f t="shared" ref="E35:E37" ca="1" si="4">TEXT(F35,G35)</f>
-        <v>01/08/26</v>
+        <v>03/21/26</v>
       </c>
       <c r="F35" s="20">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="G35" t="s">
         <v>43</v>
@@ -21443,14 +21826,14 @@
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="56"/>
+      <c r="D36" s="55"/>
       <c r="E36" s="17" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Thursday</v>
+        <v>Saturday</v>
       </c>
       <c r="F36" s="20">
         <f t="shared" ref="F36" ca="1" si="5">TODAY()</f>
-        <v>46030</v>
+        <v>46102</v>
       </c>
       <c r="G36" t="s">
         <v>44</v>
@@ -21461,14 +21844,14 @@
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="56"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="17" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>2:46 PM</v>
+        <v>2:35 PM</v>
       </c>
       <c r="F37" s="20">
         <f ca="1">NOW()</f>
-        <v>46030.615715972221</v>
+        <v>46102.60768854167</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -21507,13 +21890,13 @@
       <c r="A40" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="56" t="s">
         <v>51</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D40" s="55" t="s">
+      <c r="D40" s="56" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -21528,9 +21911,9 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="12"/>
-      <c r="B41" s="56"/>
+      <c r="B41" s="55"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="56"/>
+      <c r="D41" s="55"/>
       <c r="E41" s="17">
         <f>VALUE(F41)</f>
         <v>1000</v>
@@ -21544,7 +21927,7 @@
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="56"/>
+      <c r="D42" s="55"/>
       <c r="E42" s="17">
         <f t="shared" ref="E42" si="6">VALUE(F42)</f>
         <v>123345</v>
@@ -21575,7 +21958,7 @@
       <c r="C44" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="55" t="s">
+      <c r="D44" s="56" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -21594,7 +21977,7 @@
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="56"/>
+      <c r="D45" s="55"/>
       <c r="E45" s="17" t="str">
         <f>_xlfn.VALUETOTEXT(F45)</f>
         <v>12345.8967</v>
@@ -21608,7 +21991,7 @@
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="55" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="17" t="str">
@@ -21627,7 +22010,7 @@
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
-      <c r="D47" s="56"/>
+      <c r="D47" s="55"/>
       <c r="E47" s="17" t="str">
         <f>_xlfn.VALUETOTEXT(F47,G47)</f>
         <v>12345.8967</v>
@@ -21644,7 +22027,7 @@
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
-      <c r="D48" s="56"/>
+      <c r="D48" s="55"/>
       <c r="E48" s="6"/>
       <c r="I48" s="7"/>
     </row>
@@ -21652,7 +22035,7 @@
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
-      <c r="D49" s="56"/>
+      <c r="D49" s="55"/>
       <c r="E49" s="6"/>
       <c r="I49" s="7"/>
     </row>
@@ -21660,7 +22043,7 @@
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
-      <c r="D50" s="62"/>
+      <c r="D50" s="57"/>
       <c r="E50" s="8"/>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
@@ -21671,13 +22054,13 @@
       <c r="A51" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="61" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D51" s="63" t="s">
+      <c r="D51" s="61" t="s">
         <v>61</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -21690,9 +22073,9 @@
     </row>
     <row r="52" spans="1:9" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A52" s="12"/>
-      <c r="B52" s="64"/>
+      <c r="B52" s="62"/>
       <c r="C52" s="12"/>
-      <c r="D52" s="64"/>
+      <c r="D52" s="62"/>
       <c r="E52" s="17" t="str">
         <f>CLEAN(F52)</f>
         <v>月度报表</v>
@@ -21728,29 +22111,29 @@
       <c r="I54" s="10"/>
     </row>
     <row r="55" spans="1:9" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="66"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="67"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="65"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B56" s="55" t="s">
+      <c r="B56" s="56" t="s">
         <v>67</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D56" s="56" t="s">
         <v>68</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -21771,9 +22154,9 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="12"/>
-      <c r="B57" s="56"/>
+      <c r="B57" s="55"/>
       <c r="C57" s="12"/>
-      <c r="D57" s="56"/>
+      <c r="D57" s="55"/>
       <c r="E57" s="17" t="str">
         <f>SUBSTITUTE(F57,G57,H57)</f>
         <v>华南数据</v>
@@ -21793,7 +22176,7 @@
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
-      <c r="D58" s="56" t="s">
+      <c r="D58" s="55" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="17" t="str">
@@ -21817,7 +22200,7 @@
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
-      <c r="D59" s="56"/>
+      <c r="D59" s="55"/>
       <c r="E59" s="17" t="str">
         <f t="shared" si="7"/>
         <v>20125年2月份</v>
@@ -21839,7 +22222,7 @@
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
-      <c r="D60" s="56" t="s">
+      <c r="D60" s="55" t="s">
         <v>70</v>
       </c>
       <c r="E60" s="17" t="str">
@@ -21863,7 +22246,7 @@
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
-      <c r="D61" s="56"/>
+      <c r="D61" s="55"/>
       <c r="E61" s="6"/>
       <c r="I61" s="7"/>
     </row>
@@ -21871,7 +22254,7 @@
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
-      <c r="D62" s="56" t="s">
+      <c r="D62" s="55" t="s">
         <v>71</v>
       </c>
       <c r="E62" s="6"/>
@@ -21881,25 +22264,25 @@
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="59" t="s">
+      <c r="D63" s="55"/>
+      <c r="E63" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="F63" s="60"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="60"/>
-      <c r="I63" s="61"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="60"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="60"/>
-      <c r="G64" s="60"/>
-      <c r="H64" s="60"/>
-      <c r="I64" s="61"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="60"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" s="13"/>
@@ -21916,13 +22299,13 @@
       <c r="A66" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="55" t="s">
+      <c r="B66" s="56" t="s">
         <v>82</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="55" t="s">
+      <c r="D66" s="56" t="s">
         <v>83</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -21943,9 +22326,9 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
-      <c r="B67" s="56"/>
+      <c r="B67" s="55"/>
       <c r="C67" s="12"/>
-      <c r="D67" s="56"/>
+      <c r="D67" s="55"/>
       <c r="E67" s="17" t="str">
         <f>REPLACE(F67,G67,H67,I67)</f>
         <v>ABCD##HIJK</v>
@@ -21965,9 +22348,9 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="56"/>
+      <c r="B68" s="55"/>
       <c r="C68" s="12"/>
-      <c r="D68" s="56" t="s">
+      <c r="D68" s="55" t="s">
         <v>84</v>
       </c>
       <c r="E68" s="17" t="str">
@@ -21991,7 +22374,7 @@
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
-      <c r="D69" s="56"/>
+      <c r="D69" s="55"/>
       <c r="E69" s="17" t="str">
         <f t="shared" si="8"/>
         <v>%456</v>
@@ -22013,7 +22396,7 @@
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
-      <c r="D70" s="56"/>
+      <c r="D70" s="55"/>
       <c r="E70" s="6"/>
       <c r="I70" s="7"/>
     </row>
@@ -22021,7 +22404,7 @@
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
-      <c r="D71" s="56" t="s">
+      <c r="D71" s="55" t="s">
         <v>85</v>
       </c>
       <c r="E71" s="6"/>
@@ -22031,7 +22414,7 @@
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
-      <c r="D72" s="56"/>
+      <c r="D72" s="55"/>
       <c r="E72" s="6"/>
       <c r="I72" s="7"/>
     </row>
@@ -22039,7 +22422,7 @@
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
-      <c r="D73" s="56"/>
+      <c r="D73" s="55"/>
       <c r="E73" s="6"/>
       <c r="I73" s="7"/>
     </row>
@@ -22047,7 +22430,7 @@
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
-      <c r="D74" s="56"/>
+      <c r="D74" s="55"/>
       <c r="E74" s="6"/>
       <c r="I74" s="7"/>
     </row>
@@ -22055,7 +22438,7 @@
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
-      <c r="D75" s="56" t="s">
+      <c r="D75" s="55" t="s">
         <v>86</v>
       </c>
       <c r="E75" s="6"/>
@@ -22065,7 +22448,7 @@
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
-      <c r="D76" s="56"/>
+      <c r="D76" s="55"/>
       <c r="E76" s="6"/>
       <c r="I76" s="7"/>
     </row>
@@ -22084,7 +22467,7 @@
       <c r="A78" s="30" t="s">
         <v>741</v>
       </c>
-      <c r="B78" s="55" t="s">
+      <c r="B78" s="56" t="s">
         <v>742</v>
       </c>
       <c r="C78" s="11" t="s">
@@ -22096,18 +22479,18 @@
       <c r="E78" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F78" s="57" t="s">
+      <c r="F78" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="58"/>
+      <c r="G78" s="66"/>
+      <c r="H78" s="66"/>
+      <c r="I78" s="67"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A79" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="B79" s="56"/>
+      <c r="B79" s="55"/>
       <c r="C79" s="12"/>
       <c r="D79" s="12" t="s">
         <v>745</v>
@@ -22144,7 +22527,7 @@
       <c r="A81" s="30" t="s">
         <v>748</v>
       </c>
-      <c r="B81" s="55" t="s">
+      <c r="B81" s="56" t="s">
         <v>749</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -22167,7 +22550,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A82" s="12"/>
-      <c r="B82" s="56"/>
+      <c r="B82" s="55"/>
       <c r="C82" s="13"/>
       <c r="D82" s="12" t="s">
         <v>752</v>
@@ -22224,24 +22607,14 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="D75:D76"/>
     <mergeCell ref="D62:D64"/>
     <mergeCell ref="E63:I64"/>
     <mergeCell ref="D44:D45"/>
@@ -22253,14 +22626,24 @@
     <mergeCell ref="D56:D57"/>
     <mergeCell ref="D58:D59"/>
     <mergeCell ref="D60:D61"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22305,7 +22688,7 @@
       <c r="A2" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -22332,7 +22715,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
         <v>100</v>
@@ -22348,7 +22731,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="56"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="17">
@@ -22420,7 +22803,7 @@
       <c r="A8" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="56" t="s">
         <v>111</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -22445,7 +22828,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="12"/>
-      <c r="B9" s="56"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="s">
         <v>116</v>
@@ -22468,10 +22851,10 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="55" t="s">
         <v>119</v>
       </c>
       <c r="E10" s="6"/>
@@ -22486,8 +22869,8 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
       <c r="E11" s="17">
         <f>SUMIF(H9:H13,G11)</f>
         <v>4</v>
@@ -22506,8 +22889,8 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="6"/>
       <c r="F12" t="s">
         <v>108</v>
@@ -22520,8 +22903,8 @@
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="6"/>
       <c r="F13" t="s">
         <v>114</v>
@@ -22534,8 +22917,8 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="6"/>
       <c r="I14" s="7"/>
     </row>
@@ -22554,13 +22937,13 @@
       <c r="A16" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="56" t="s">
         <v>130</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -22581,9 +22964,9 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="17">
         <f>SUMIFS(F17:F21,H17:H21,G17,I17:I21,G19)</f>
         <v>5</v>
@@ -22605,7 +22988,7 @@
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="56"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="6"/>
       <c r="F18">
         <v>2</v>
@@ -22624,7 +23007,7 @@
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E19" s="6"/>
@@ -22645,7 +23028,7 @@
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="56"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="6"/>
       <c r="F20">
         <v>2</v>
@@ -22661,7 +23044,7 @@
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="56"/>
+      <c r="D21" s="55"/>
       <c r="E21" s="6"/>
       <c r="F21">
         <v>5</v>
@@ -22688,7 +23071,7 @@
       <c r="A23" s="30" t="s">
         <v>712</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="56" t="s">
         <v>713</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -22700,18 +23083,18 @@
       <c r="E23" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="58"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="12"/>
-      <c r="B24" s="56"/>
+      <c r="B24" s="55"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="56" t="s">
+      <c r="D24" s="55" t="s">
         <v>715</v>
       </c>
       <c r="E24" s="17">
@@ -22734,10 +23117,10 @@
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="55" t="s">
         <v>716</v>
       </c>
-      <c r="D25" s="56"/>
+      <c r="D25" s="55"/>
       <c r="E25" s="17">
         <f>SUMPRODUCT(F25:I25)</f>
         <v>10</v>
@@ -22758,8 +23141,8 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
       <c r="E26" s="17">
         <f>SUMPRODUCT(F26:I26)</f>
         <v>26</v>
@@ -22780,8 +23163,8 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
       <c r="E27" s="17">
         <f>SUMPRODUCT(F25:I25,F26:I26)</f>
         <v>70</v>
@@ -22841,30 +23224,30 @@
       <c r="A31" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="56" t="s">
         <v>136</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="56" t="s">
         <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="58"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="12"/>
-      <c r="B32" s="56"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="56"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="17">
         <f>COUNT(F32:I32)</f>
         <v>1</v>
@@ -22881,9 +23264,9 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="12"/>
-      <c r="B33" s="56"/>
+      <c r="B33" s="55"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="56"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="17">
         <f>COUNT("A","#",3)</f>
         <v>1</v>
@@ -22894,7 +23277,7 @@
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="56" t="s">
+      <c r="D34" s="55" t="s">
         <v>139</v>
       </c>
       <c r="E34" s="6"/>
@@ -22904,7 +23287,7 @@
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="56"/>
+      <c r="D35" s="55"/>
       <c r="E35" s="6"/>
       <c r="I35" s="7"/>
     </row>
@@ -22923,30 +23306,30 @@
       <c r="A37" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="56" t="s">
         <v>142</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="55" t="s">
+      <c r="D37" s="56" t="s">
         <v>138</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="67"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="12"/>
-      <c r="B38" s="56"/>
+      <c r="B38" s="55"/>
       <c r="C38" s="12"/>
-      <c r="D38" s="56"/>
+      <c r="D38" s="55"/>
       <c r="E38" s="17">
         <f>COUNTA(F38:I38)</f>
         <v>3</v>
@@ -22965,7 +23348,7 @@
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="56"/>
+      <c r="D39" s="55"/>
       <c r="E39" s="17">
         <f>COUNTA("A","#",3)</f>
         <v>3</v>
@@ -22976,7 +23359,7 @@
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="56" t="s">
+      <c r="D40" s="55" t="s">
         <v>139</v>
       </c>
       <c r="E40" s="6"/>
@@ -22986,7 +23369,7 @@
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="56"/>
+      <c r="D41" s="55"/>
       <c r="E41" s="6"/>
       <c r="I41" s="7"/>
     </row>
@@ -23005,30 +23388,30 @@
       <c r="A43" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="56" t="s">
         <v>142</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D43" s="55" t="s">
+      <c r="D43" s="56" t="s">
         <v>145</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="57" t="s">
+      <c r="F43" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="58"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="67"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="12"/>
-      <c r="B44" s="56"/>
+      <c r="B44" s="55"/>
       <c r="C44" s="12"/>
-      <c r="D44" s="56"/>
+      <c r="D44" s="55"/>
       <c r="E44" s="17">
         <f>COUNTBLANK(F44:I44)</f>
         <v>1</v>
@@ -23047,7 +23430,7 @@
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="56" t="s">
+      <c r="D45" s="55" t="s">
         <v>146</v>
       </c>
       <c r="E45" s="6"/>
@@ -23057,7 +23440,7 @@
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
-      <c r="D46" s="70"/>
+      <c r="D46" s="69"/>
       <c r="E46" s="6"/>
       <c r="I46" s="7"/>
     </row>
@@ -23076,30 +23459,30 @@
       <c r="A48" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="56" t="s">
         <v>185</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="55" t="s">
+      <c r="D48" s="56" t="s">
         <v>196</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F48" s="57" t="s">
+      <c r="F48" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="58"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="12"/>
-      <c r="B49" s="56"/>
+      <c r="B49" s="55"/>
       <c r="C49" s="12"/>
-      <c r="D49" s="56"/>
+      <c r="D49" s="55"/>
       <c r="E49" s="17">
         <f>COUNTIF(F49:H49,I49)</f>
         <v>2</v>
@@ -23121,7 +23504,7 @@
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
-      <c r="D50" s="56"/>
+      <c r="D50" s="55"/>
       <c r="E50" s="17">
         <f>COUNTIF(F50:H50,"&lt;&gt;"&amp;I50)</f>
         <v>2</v>
@@ -23143,7 +23526,7 @@
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
-      <c r="D51" s="56" t="s">
+      <c r="D51" s="55" t="s">
         <v>200</v>
       </c>
       <c r="E51" s="17">
@@ -23167,7 +23550,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
-      <c r="D52" s="56"/>
+      <c r="D52" s="55"/>
       <c r="E52" s="17">
         <f>COUNTIF(F52:I52,"*")</f>
         <v>4</v>
@@ -23189,7 +23572,7 @@
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
-      <c r="D53" s="56"/>
+      <c r="D53" s="55"/>
       <c r="E53" s="17">
         <f>COUNTIF(F53:I53,"?南")</f>
         <v>3</v>
@@ -23222,13 +23605,13 @@
       <c r="A55" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="B55" s="55" t="s">
+      <c r="B55" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="C55" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="56" t="s">
         <v>194</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -23249,9 +23632,9 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="12"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
       <c r="E56" s="19">
         <f>COUNTIFS(F56:F63,G56,H56:H63,"?南",I56:I63,"&gt;="&amp;100)</f>
         <v>2</v>
@@ -23273,7 +23656,7 @@
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
-      <c r="D57" s="56"/>
+      <c r="D57" s="55"/>
       <c r="F57" t="s">
         <v>205</v>
       </c>
@@ -23288,7 +23671,7 @@
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
-      <c r="D58" s="56" t="s">
+      <c r="D58" s="55" t="s">
         <v>195</v>
       </c>
       <c r="F58" t="s">
@@ -23305,7 +23688,7 @@
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
-      <c r="D59" s="56"/>
+      <c r="D59" s="55"/>
       <c r="F59" t="s">
         <v>206</v>
       </c>
@@ -23320,7 +23703,7 @@
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
-      <c r="D60" s="56"/>
+      <c r="D60" s="55"/>
       <c r="F60" t="s">
         <v>204</v>
       </c>
@@ -23335,7 +23718,7 @@
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
-      <c r="D61" s="56" t="s">
+      <c r="D61" s="55" t="s">
         <v>198</v>
       </c>
       <c r="F61" t="s">
@@ -23352,7 +23735,7 @@
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
-      <c r="D62" s="56"/>
+      <c r="D62" s="55"/>
       <c r="F62" t="s">
         <v>204</v>
       </c>
@@ -23367,7 +23750,7 @@
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
-      <c r="D63" s="56"/>
+      <c r="D63" s="55"/>
       <c r="F63" t="s">
         <v>207</v>
       </c>
@@ -23401,24 +23784,24 @@
       <c r="C65" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D65" s="55" t="s">
+      <c r="D65" s="56" t="s">
         <v>214</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="58"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="66"/>
+      <c r="I65" s="67"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
-      <c r="D66" s="56"/>
+      <c r="D66" s="55"/>
       <c r="E66" s="17">
         <f>MAX(F66:I66)</f>
         <v>5</v>
@@ -23440,7 +23823,7 @@
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
-      <c r="D67" s="56"/>
+      <c r="D67" s="55"/>
       <c r="E67" s="17">
         <f>MAX(F67:G67,H67:I67)</f>
         <v>5</v>
@@ -23499,7 +23882,7 @@
       <c r="A71" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="B71" s="55" t="s">
+      <c r="B71" s="56" t="s">
         <v>217</v>
       </c>
       <c r="C71" s="11" t="s">
@@ -23511,18 +23894,18 @@
       <c r="E71" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F71" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="58"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="66"/>
+      <c r="I71" s="67"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A72" s="12"/>
-      <c r="B72" s="56"/>
+      <c r="B72" s="55"/>
       <c r="C72" s="12"/>
-      <c r="D72" s="56" t="s">
+      <c r="D72" s="55" t="s">
         <v>220</v>
       </c>
       <c r="E72" s="17">
@@ -23546,7 +23929,7 @@
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
-      <c r="D73" s="56"/>
+      <c r="D73" s="55"/>
       <c r="E73" s="17">
         <f>AVERAGE(F73:G73,H73:I73)</f>
         <v>2.75</v>
@@ -23579,7 +23962,7 @@
       <c r="A75" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B75" s="55" t="s">
+      <c r="B75" s="56" t="s">
         <v>221</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -23604,9 +23987,9 @@
     </row>
     <row r="76" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="12"/>
-      <c r="B76" s="56"/>
+      <c r="B76" s="55"/>
       <c r="C76" s="12"/>
-      <c r="D76" s="56" t="s">
+      <c r="D76" s="55" t="s">
         <v>224</v>
       </c>
       <c r="E76" s="17">
@@ -23626,9 +24009,9 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A77" s="12"/>
-      <c r="B77" s="56"/>
+      <c r="B77" s="55"/>
       <c r="C77" s="12"/>
-      <c r="D77" s="56"/>
+      <c r="D77" s="55"/>
       <c r="E77" s="6"/>
       <c r="F77" t="s">
         <v>93</v>
@@ -23642,7 +24025,7 @@
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
-      <c r="D78" s="56"/>
+      <c r="D78" s="55"/>
       <c r="E78" s="17">
         <f>AVERAGEIF(H76:H80,"&gt;"&amp;3,H76:H80)</f>
         <v>4.5</v>
@@ -23659,7 +24042,7 @@
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
-      <c r="D79" s="56" t="s">
+      <c r="D79" s="55" t="s">
         <v>225</v>
       </c>
       <c r="E79" s="6"/>
@@ -23675,7 +24058,7 @@
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
-      <c r="D80" s="56"/>
+      <c r="D80" s="55"/>
       <c r="E80" s="17">
         <f>AVERAGEIF(H76:H80,"&gt;"&amp;3)</f>
         <v>4.5</v>
@@ -23703,10 +24086,10 @@
       <c r="A82" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B82" s="55" t="s">
+      <c r="B82" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C82" s="55" t="s">
+      <c r="C82" s="56" t="s">
         <v>230</v>
       </c>
       <c r="D82" s="11" t="s">
@@ -23730,8 +24113,8 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A83" s="12"/>
-      <c r="B83" s="56"/>
-      <c r="C83" s="56"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="55"/>
       <c r="D83" s="12" t="s">
         <v>232</v>
       </c>
@@ -23754,9 +24137,9 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A84" s="12"/>
-      <c r="B84" s="56"/>
+      <c r="B84" s="55"/>
       <c r="C84" s="12"/>
-      <c r="D84" s="56" t="s">
+      <c r="D84" s="55" t="s">
         <v>233</v>
       </c>
       <c r="E84" s="6"/>
@@ -23774,7 +24157,7 @@
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
-      <c r="D85" s="56"/>
+      <c r="D85" s="55"/>
       <c r="E85" s="6"/>
       <c r="F85">
         <v>3</v>
@@ -23837,30 +24220,30 @@
       <c r="A89" s="30" t="s">
         <v>635</v>
       </c>
-      <c r="B89" s="55" t="s">
+      <c r="B89" s="56" t="s">
         <v>642</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="D89" s="55" t="s">
+      <c r="D89" s="56" t="s">
         <v>637</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F89" s="57" t="s">
+      <c r="F89" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G89" s="57"/>
-      <c r="H89" s="57"/>
-      <c r="I89" s="58"/>
+      <c r="G89" s="66"/>
+      <c r="H89" s="66"/>
+      <c r="I89" s="67"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A90" s="12"/>
-      <c r="B90" s="56"/>
+      <c r="B90" s="55"/>
       <c r="C90" s="12"/>
-      <c r="D90" s="56"/>
+      <c r="D90" s="55"/>
       <c r="E90" s="17">
         <f>MEDIAN(F90:H90)</f>
         <v>3</v>
@@ -23915,7 +24298,7 @@
       <c r="A93" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="B93" s="55" t="s">
+      <c r="B93" s="56" t="s">
         <v>643</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -23927,20 +24310,20 @@
       <c r="E93" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="58"/>
+      <c r="G93" s="66"/>
+      <c r="H93" s="66"/>
+      <c r="I93" s="67"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A94" s="56" t="s">
+      <c r="A94" s="55" t="s">
         <v>640</v>
       </c>
-      <c r="B94" s="56"/>
+      <c r="B94" s="55"/>
       <c r="C94" s="12"/>
-      <c r="D94" s="56" t="s">
+      <c r="D94" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E94" s="17" t="e">
@@ -23961,10 +24344,10 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A95" s="56"/>
-      <c r="B95" s="56"/>
+      <c r="A95" s="55"/>
+      <c r="B95" s="55"/>
       <c r="C95" s="12"/>
-      <c r="D95" s="56"/>
+      <c r="D95" s="55"/>
       <c r="E95" s="17">
         <f>MODE(F95:I95)</f>
         <v>2</v>
@@ -23997,7 +24380,7 @@
       <c r="A97" s="30" t="s">
         <v>645</v>
       </c>
-      <c r="B97" s="55" t="s">
+      <c r="B97" s="56" t="s">
         <v>644</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -24009,18 +24392,18 @@
       <c r="E97" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="58"/>
+      <c r="G97" s="66"/>
+      <c r="H97" s="66"/>
+      <c r="I97" s="67"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A98" s="12"/>
-      <c r="B98" s="56"/>
+      <c r="B98" s="55"/>
       <c r="C98" s="12"/>
-      <c r="D98" s="56" t="s">
+      <c r="D98" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E98" s="17" t="e">
@@ -24042,9 +24425,9 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A99" s="12"/>
-      <c r="B99" s="56"/>
+      <c r="B99" s="55"/>
       <c r="C99" s="12"/>
-      <c r="D99" s="56"/>
+      <c r="D99" s="55"/>
       <c r="E99" s="17">
         <f>_xlfn.MODE.SNGL(F99:I99)</f>
         <v>2</v>
@@ -24118,7 +24501,7 @@
       <c r="A103" s="31" t="s">
         <v>647</v>
       </c>
-      <c r="B103" s="55" t="s">
+      <c r="B103" s="56" t="s">
         <v>648</v>
       </c>
       <c r="C103" s="12" t="s">
@@ -24130,20 +24513,20 @@
       <c r="E103" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F103" s="57" t="s">
+      <c r="F103" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G103" s="57"/>
-      <c r="H103" s="57"/>
-      <c r="I103" s="58"/>
+      <c r="G103" s="66"/>
+      <c r="H103" s="66"/>
+      <c r="I103" s="67"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" s="12"/>
-      <c r="B104" s="56"/>
+      <c r="B104" s="55"/>
       <c r="C104" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="D104" s="56" t="s">
+      <c r="D104" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E104" s="17" t="e" cm="1">
@@ -24165,11 +24548,11 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A105" s="12"/>
-      <c r="B105" s="56"/>
+      <c r="B105" s="55"/>
       <c r="C105" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="D105" s="56"/>
+      <c r="D105" s="55"/>
       <c r="E105" s="17" cm="1">
         <f t="array" ref="E105">_xlfn.MODE.MULT(F105:I105)</f>
         <v>2</v>
@@ -24189,7 +24572,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A106" s="12"/>
-      <c r="B106" s="56"/>
+      <c r="B106" s="55"/>
       <c r="C106" s="12"/>
       <c r="D106" s="12"/>
       <c r="E106" s="48" cm="1">
@@ -24283,7 +24666,7 @@
       <c r="A111" s="30" t="s">
         <v>652</v>
       </c>
-      <c r="B111" s="55" t="s">
+      <c r="B111" s="56" t="s">
         <v>653</v>
       </c>
       <c r="C111" s="11" t="s">
@@ -24295,20 +24678,20 @@
       <c r="E111" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F111" s="57" t="s">
+      <c r="F111" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G111" s="57"/>
-      <c r="H111" s="57"/>
-      <c r="I111" s="58"/>
+      <c r="G111" s="66"/>
+      <c r="H111" s="66"/>
+      <c r="I111" s="67"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A112" s="12"/>
-      <c r="B112" s="56"/>
+      <c r="B112" s="55"/>
       <c r="C112" s="68" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="D112" s="56" t="s">
+      <c r="D112" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E112" s="17">
@@ -24330,9 +24713,9 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A113" s="12"/>
-      <c r="B113" s="56"/>
+      <c r="B113" s="55"/>
       <c r="C113" s="68"/>
-      <c r="D113" s="56"/>
+      <c r="D113" s="55"/>
       <c r="E113" s="6"/>
       <c r="F113">
         <v>5</v>
@@ -24350,7 +24733,7 @@
     <row r="114" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A114" s="12"/>
       <c r="B114" s="15"/>
-      <c r="C114" s="56" t="s">
+      <c r="C114" s="55" t="s">
         <v>656</v>
       </c>
       <c r="D114" s="15"/>
@@ -24371,7 +24754,7 @@
     <row r="115" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A115" s="12"/>
       <c r="B115" s="15"/>
-      <c r="C115" s="56"/>
+      <c r="C115" s="55"/>
       <c r="D115" s="15"/>
       <c r="E115" s="6"/>
       <c r="F115">
@@ -24402,7 +24785,7 @@
       <c r="A117" s="30" t="s">
         <v>657</v>
       </c>
-      <c r="B117" s="55" t="s">
+      <c r="B117" s="56" t="s">
         <v>658</v>
       </c>
       <c r="C117" s="11" t="s">
@@ -24414,20 +24797,20 @@
       <c r="E117" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F117" s="57" t="s">
+      <c r="F117" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G117" s="57"/>
-      <c r="H117" s="57"/>
-      <c r="I117" s="58"/>
+      <c r="G117" s="66"/>
+      <c r="H117" s="66"/>
+      <c r="I117" s="67"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A118" s="12"/>
-      <c r="B118" s="56"/>
-      <c r="C118" s="69" t="e" vm="9">
+      <c r="B118" s="55"/>
+      <c r="C118" s="70" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="D118" s="56" t="s">
+      <c r="D118" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E118" s="17">
@@ -24449,9 +24832,9 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A119" s="12"/>
-      <c r="B119" s="56"/>
-      <c r="C119" s="69"/>
-      <c r="D119" s="56"/>
+      <c r="B119" s="55"/>
+      <c r="C119" s="70"/>
+      <c r="D119" s="55"/>
       <c r="E119" s="6"/>
       <c r="F119">
         <v>5</v>
@@ -24468,8 +24851,8 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A120" s="12"/>
-      <c r="B120" s="56"/>
-      <c r="C120" s="56" t="s">
+      <c r="B120" s="55"/>
+      <c r="C120" s="55" t="s">
         <v>660</v>
       </c>
       <c r="D120" s="12"/>
@@ -24490,7 +24873,7 @@
     <row r="121" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
-      <c r="C121" s="56"/>
+      <c r="C121" s="55"/>
       <c r="D121" s="12"/>
       <c r="E121" s="6"/>
       <c r="F121">
@@ -24521,7 +24904,7 @@
       <c r="A123" s="30" t="s">
         <v>721</v>
       </c>
-      <c r="B123" s="55" t="s">
+      <c r="B123" s="56" t="s">
         <v>720</v>
       </c>
       <c r="C123" s="11" t="s">
@@ -24533,20 +24916,20 @@
       <c r="E123" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F123" s="57" t="s">
+      <c r="F123" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G123" s="57"/>
-      <c r="H123" s="57"/>
-      <c r="I123" s="58"/>
+      <c r="G123" s="66"/>
+      <c r="H123" s="66"/>
+      <c r="I123" s="67"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A124" s="12"/>
-      <c r="B124" s="56"/>
+      <c r="B124" s="55"/>
       <c r="C124" s="68" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="D124" s="56" t="s">
+      <c r="D124" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E124" s="17">
@@ -24568,9 +24951,9 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A125" s="12"/>
-      <c r="B125" s="56"/>
+      <c r="B125" s="55"/>
       <c r="C125" s="68"/>
-      <c r="D125" s="56"/>
+      <c r="D125" s="55"/>
       <c r="E125" s="6"/>
       <c r="F125">
         <v>5</v>
@@ -24588,7 +24971,7 @@
     <row r="126" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
-      <c r="C126" s="56" t="s">
+      <c r="C126" s="55" t="s">
         <v>722</v>
       </c>
       <c r="D126" s="12"/>
@@ -24609,7 +24992,7 @@
     <row r="127" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
-      <c r="C127" s="56"/>
+      <c r="C127" s="55"/>
       <c r="D127" s="12"/>
       <c r="E127" s="6"/>
       <c r="F127">
@@ -24640,7 +25023,7 @@
       <c r="A129" s="31" t="s">
         <v>723</v>
       </c>
-      <c r="B129" s="55" t="s">
+      <c r="B129" s="56" t="s">
         <v>725</v>
       </c>
       <c r="C129" s="12" t="s">
@@ -24652,20 +25035,20 @@
       <c r="E129" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F129" s="57" t="s">
+      <c r="F129" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="G129" s="57"/>
-      <c r="H129" s="57"/>
-      <c r="I129" s="58"/>
+      <c r="G129" s="66"/>
+      <c r="H129" s="66"/>
+      <c r="I129" s="67"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A130" s="12"/>
-      <c r="B130" s="56"/>
+      <c r="B130" s="55"/>
       <c r="C130" s="68" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="D130" s="56" t="s">
+      <c r="D130" s="55" t="s">
         <v>655</v>
       </c>
       <c r="E130" s="17">
@@ -24687,9 +25070,9 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A131" s="12"/>
-      <c r="B131" s="56"/>
+      <c r="B131" s="55"/>
       <c r="C131" s="68"/>
-      <c r="D131" s="56"/>
+      <c r="D131" s="55"/>
       <c r="E131" s="6"/>
       <c r="F131">
         <v>5</v>
@@ -24707,7 +25090,7 @@
     <row r="132" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
-      <c r="C132" s="56" t="s">
+      <c r="C132" s="55" t="s">
         <v>726</v>
       </c>
       <c r="D132" s="12"/>
@@ -24728,7 +25111,7 @@
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
-      <c r="C133" s="56"/>
+      <c r="C133" s="55"/>
       <c r="D133" s="12"/>
       <c r="E133" s="6"/>
       <c r="F133">
@@ -24784,7 +25167,7 @@
       <c r="A137" s="31" t="s">
         <v>664</v>
       </c>
-      <c r="B137" s="55" t="s">
+      <c r="B137" s="56" t="s">
         <v>663</v>
       </c>
       <c r="C137" s="12" t="s">
@@ -24796,16 +25179,16 @@
       <c r="E137" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F137" s="57" t="s">
+      <c r="F137" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="G137" s="57"/>
-      <c r="H137" s="57"/>
-      <c r="I137" s="58"/>
+      <c r="G137" s="66"/>
+      <c r="H137" s="66"/>
+      <c r="I137" s="67"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A138" s="12"/>
-      <c r="B138" s="56"/>
+      <c r="B138" s="55"/>
       <c r="C138" s="12"/>
       <c r="D138" s="12" t="s">
         <v>667</v>
@@ -24861,13 +25244,13 @@
       <c r="A141" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="B141" s="55" t="s">
+      <c r="B141" s="56" t="s">
         <v>385</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D141" s="55" t="s">
+      <c r="D141" s="56" t="s">
         <v>386</v>
       </c>
       <c r="E141" s="3" t="s">
@@ -24886,9 +25269,9 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A142" s="12"/>
-      <c r="B142" s="56"/>
+      <c r="B142" s="55"/>
       <c r="C142" s="12"/>
-      <c r="D142" s="56"/>
+      <c r="D142" s="55"/>
       <c r="E142" s="17">
         <f>RANK(F142,G142:G146)</f>
         <v>4</v>
@@ -24907,7 +25290,7 @@
       <c r="C143" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="D143" s="56" t="s">
+      <c r="D143" s="55" t="s">
         <v>387</v>
       </c>
       <c r="E143" s="17">
@@ -24928,7 +25311,7 @@
       <c r="C144" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="D144" s="56"/>
+      <c r="D144" s="55"/>
       <c r="E144" s="17">
         <f>RANK(F144,G142:G146,H144)</f>
         <v>4</v>
@@ -24982,7 +25365,7 @@
       <c r="A147" s="30" t="s">
         <v>727</v>
       </c>
-      <c r="B147" s="55" t="s">
+      <c r="B147" s="56" t="s">
         <v>728</v>
       </c>
       <c r="C147" s="11" t="s">
@@ -24997,15 +25380,15 @@
       <c r="F147" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="G147" s="57" t="s">
+      <c r="G147" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="H147" s="57"/>
-      <c r="I147" s="58"/>
+      <c r="H147" s="66"/>
+      <c r="I147" s="67"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A148" s="12"/>
-      <c r="B148" s="56"/>
+      <c r="B148" s="55"/>
       <c r="C148" s="12"/>
       <c r="D148" t="s">
         <v>730</v>
@@ -25042,7 +25425,7 @@
       <c r="A150" s="31" t="s">
         <v>733</v>
       </c>
-      <c r="B150" s="55" t="s">
+      <c r="B150" s="56" t="s">
         <v>734</v>
       </c>
       <c r="C150" s="12" t="s">
@@ -25057,15 +25440,15 @@
       <c r="F150" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="G150" s="57" t="s">
+      <c r="G150" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="H150" s="57"/>
-      <c r="I150" s="58"/>
+      <c r="H150" s="66"/>
+      <c r="I150" s="67"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A151" s="12"/>
-      <c r="B151" s="56"/>
+      <c r="B151" s="55"/>
       <c r="C151" s="12"/>
       <c r="D151" t="s">
         <v>736</v>
@@ -25098,7 +25481,7 @@
       <c r="A153" s="30" t="s">
         <v>669</v>
       </c>
-      <c r="B153" s="55" t="s">
+      <c r="B153" s="56" t="s">
         <v>668</v>
       </c>
       <c r="C153" s="11" t="s">
@@ -25110,18 +25493,18 @@
       <c r="E153" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F153" s="57" t="s">
+      <c r="F153" s="66" t="s">
         <v>389</v>
       </c>
-      <c r="G153" s="57"/>
-      <c r="H153" s="57"/>
-      <c r="I153" s="58"/>
+      <c r="G153" s="66"/>
+      <c r="H153" s="66"/>
+      <c r="I153" s="67"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A154" s="12"/>
-      <c r="B154" s="56"/>
+      <c r="B154" s="55"/>
       <c r="C154" s="12"/>
-      <c r="D154" s="56" t="s">
+      <c r="D154" s="55" t="s">
         <v>688</v>
       </c>
       <c r="E154" s="17">
@@ -25146,7 +25529,7 @@
       <c r="A155" s="13"/>
       <c r="B155" s="16"/>
       <c r="C155" s="13"/>
-      <c r="D155" s="56"/>
+      <c r="D155" s="55"/>
       <c r="E155" s="6" t="s">
         <v>684</v>
       </c>
@@ -25495,6 +25878,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="G147:I147"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="G150:I150"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="F137:I137"/>
+    <mergeCell ref="D143:D144"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="F153:I153"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F123:I123"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="F129:I129"/>
+    <mergeCell ref="F117:I117"/>
+    <mergeCell ref="B117:B120"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="F111:I111"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="F93:I93"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="F103:I103"/>
     <mergeCell ref="D130:D131"/>
     <mergeCell ref="B71:B72"/>
     <mergeCell ref="D72:D73"/>
@@ -25511,79 +25967,6 @@
     <mergeCell ref="B137:B138"/>
     <mergeCell ref="B129:B131"/>
     <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="F89:I89"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="F93:I93"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="B97:B99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="F97:I97"/>
-    <mergeCell ref="F103:I103"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="F111:I111"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="F153:I153"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F123:I123"/>
-    <mergeCell ref="B123:B125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="F129:I129"/>
-    <mergeCell ref="F117:I117"/>
-    <mergeCell ref="B117:B120"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="G147:I147"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="G150:I150"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="F137:I137"/>
-    <mergeCell ref="D143:D144"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25627,13 +26010,13 @@
       <c r="A2" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="E2" s="3" t="s">
         <v>109</v>
       </c>
@@ -25652,9 +26035,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="13"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="17">
         <f>_xlfn.XLOOKUP(F3,G3:G7,H3:H7)</f>
         <v>3</v>
@@ -25856,7 +26239,7 @@
       <c r="A19" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="59" t="s">
         <v>256</v>
       </c>
       <c r="C19" t="s">
@@ -25866,7 +26249,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
-      <c r="B20" s="60"/>
+      <c r="B20" s="59"/>
       <c r="C20" t="s">
         <v>257</v>
       </c>
@@ -25901,7 +26284,7 @@
       <c r="A24" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="56" t="s">
         <v>275</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -25924,9 +26307,9 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="12"/>
-      <c r="B25" s="56"/>
+      <c r="B25" s="55"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="56" t="s">
+      <c r="D25" s="55" t="s">
         <v>279</v>
       </c>
       <c r="E25" s="17" cm="1">
@@ -25944,10 +26327,10 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="55" t="s">
         <v>277</v>
       </c>
-      <c r="D26" s="56"/>
+      <c r="D26" s="55"/>
       <c r="E26" s="17" cm="1">
         <f t="array" aca="1" ref="E26" ca="1">INDIRECT(F26&amp;26)</f>
         <v>0</v>
@@ -25963,8 +26346,8 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
       <c r="E27" s="17" cm="1">
         <f t="array" aca="1" ref="E27" ca="1">INDIRECT("H"&amp;F27)</f>
         <v>333</v>
@@ -25980,7 +26363,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
-      <c r="C28" s="56"/>
+      <c r="C28" s="55"/>
       <c r="D28" s="12" t="s">
         <v>280</v>
       </c>
@@ -26042,7 +26425,7 @@
       <c r="C31" s="11" t="s">
         <v>761</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="56" t="s">
         <v>762</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -26057,7 +26440,7 @@
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="56"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="17">
         <f>ROW()</f>
         <v>32</v>
@@ -26068,7 +26451,7 @@
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="56"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="17">
         <f>ROW(F32)</f>
         <v>32</v>
@@ -26128,7 +26511,7 @@
       <c r="C38" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="D38" s="55" t="s">
+      <c r="D38" s="56" t="s">
         <v>766</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -26143,7 +26526,7 @@
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="56"/>
+      <c r="D39" s="55"/>
       <c r="E39" s="17">
         <f>ROWS(F38:I39)</f>
         <v>2</v>
@@ -26216,23 +26599,23 @@
       <c r="I44" s="10"/>
     </row>
     <row r="45" spans="1:9" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="67"/>
+      <c r="B45" s="64"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="65"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="56" t="s">
         <v>261</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -26244,18 +26627,18 @@
       <c r="E46" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F46" s="57" t="s">
+      <c r="F46" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
       <c r="I46" s="5" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="12"/>
-      <c r="B47" s="56"/>
+      <c r="B47" s="55"/>
       <c r="C47" s="7"/>
       <c r="D47" s="12"/>
       <c r="E47" s="35" cm="1">
@@ -26277,7 +26660,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="12"/>
-      <c r="B48" s="56"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="7"/>
       <c r="D48" s="12"/>
       <c r="E48" s="17" cm="1">
@@ -26299,7 +26682,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="12"/>
-      <c r="B49" s="56"/>
+      <c r="B49" s="55"/>
       <c r="C49" s="7"/>
       <c r="D49" s="12"/>
       <c r="E49" s="17" cm="1">
@@ -26321,10 +26704,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="12"/>
-      <c r="B50" s="56" t="s">
+      <c r="B50" s="55" t="s">
         <v>267</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="55" t="s">
         <v>268</v>
       </c>
       <c r="D50" s="12" t="s">
@@ -26342,8 +26725,8 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="12"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
       <c r="D51" s="12"/>
       <c r="E51" s="19" cm="1">
         <f t="array" ref="E51">INDEX(F51:I58,E54,E56)</f>
@@ -26364,7 +26747,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="12"/>
-      <c r="B52" s="56"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="12"/>
       <c r="D52" s="12"/>
       <c r="E52" s="19" cm="1">
@@ -26386,7 +26769,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="12"/>
-      <c r="B53" s="56"/>
+      <c r="B53" s="55"/>
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
       <c r="E53" t="s">
@@ -26407,7 +26790,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="12"/>
-      <c r="B54" s="56"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
       <c r="E54">
@@ -26525,7 +26908,7 @@
       <c r="A60" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="55" t="s">
+      <c r="B60" s="56" t="s">
         <v>272</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -26540,15 +26923,15 @@
       <c r="F60" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G60" s="57" t="s">
+      <c r="G60" s="66" t="s">
         <v>273</v>
       </c>
-      <c r="H60" s="57"/>
-      <c r="I60" s="58"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="67"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" s="12"/>
-      <c r="B61" s="56"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="12"/>
       <c r="D61" s="12"/>
       <c r="E61" s="17">
@@ -26570,7 +26953,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" s="12"/>
-      <c r="B62" s="56"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="12"/>
       <c r="D62" s="12"/>
       <c r="E62" s="17">
@@ -26625,6 +27008,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D38:D39"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="G60:I60"/>
@@ -26634,14 +27025,6 @@
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="F46:H46"/>
     <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="D38:D39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26685,7 +27068,7 @@
       <c r="A2" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>295</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -26712,7 +27095,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="12"/>
       <c r="D3" s="15" t="s">
         <v>297</v>
@@ -26771,13 +27154,13 @@
       <c r="A6" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="56" t="s">
         <v>305</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="56" t="s">
         <v>306</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="56" t="s">
         <v>307</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -26792,9 +27175,9 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="12"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="17" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(F7&gt;G8,H7,F7&gt;G10,H9,F7&gt;G12,H11,F7&lt;G12,H13)</f>
         <v>A</v>
@@ -26809,7 +27192,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="12"/>
-      <c r="B8" s="56"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
         <v>308</v>
@@ -26824,7 +27207,7 @@
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="55" t="s">
         <v>309</v>
       </c>
       <c r="E9" s="17" t="str" cm="1">
@@ -26843,7 +27226,7 @@
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="56"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="6"/>
       <c r="G10">
         <v>60</v>
@@ -26854,7 +27237,7 @@
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="56" t="s">
+      <c r="D11" s="55" t="s">
         <v>310</v>
       </c>
       <c r="E11" s="17" t="str" cm="1">
@@ -26873,7 +27256,7 @@
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="56"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="6"/>
       <c r="G12">
         <v>0</v>
@@ -26918,7 +27301,7 @@
       <c r="C15" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="56" t="s">
         <v>313</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -26937,7 +27320,7 @@
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="56"/>
+      <c r="D16" s="55"/>
       <c r="E16" s="17" t="e">
         <f>F16</f>
         <v>#DIV/0!</v>
@@ -26951,10 +27334,10 @@
     <row r="17" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="55" t="s">
         <v>315</v>
       </c>
-      <c r="D17" s="56" t="s">
+      <c r="D17" s="55" t="s">
         <v>314</v>
       </c>
       <c r="E17" s="17">
@@ -26973,8 +27356,8 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="17" t="e">
         <f>F18</f>
         <v>#NAME?</v>
@@ -26989,7 +27372,7 @@
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="15"/>
-      <c r="D19" s="56"/>
+      <c r="D19" s="55"/>
       <c r="E19" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -27018,7 +27401,7 @@
       <c r="A21" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="56" t="s">
         <v>318</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -27041,9 +27424,9 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="12"/>
-      <c r="B22" s="56"/>
+      <c r="B22" s="55"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="56" t="s">
+      <c r="D22" s="55" t="s">
         <v>323</v>
       </c>
       <c r="E22" s="17" t="b">
@@ -27062,7 +27445,7 @@
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="56"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="17" t="b">
         <f t="shared" ref="E23:E24" si="1">AND(F23,G23)</f>
         <v>0</v>
@@ -27107,7 +27490,7 @@
       <c r="A26" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="56" t="s">
         <v>318</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -27130,9 +27513,9 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="12"/>
-      <c r="B27" s="56"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="55" t="s">
         <v>323</v>
       </c>
       <c r="E27" s="17" t="b">
@@ -27151,7 +27534,7 @@
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="56"/>
+      <c r="D28" s="55"/>
       <c r="E28" s="17" t="b">
         <f t="shared" ref="E28:E29" si="2">OR(F28,G28)</f>
         <v>1</v>
@@ -27202,7 +27585,7 @@
       <c r="C31" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="56" t="s">
         <v>326</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -27219,7 +27602,7 @@
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="56"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="17" t="b">
         <f>NOT(F32)</f>
         <v>0</v>
@@ -27233,7 +27616,7 @@
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="56"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="17" t="b">
         <f>NOT(F33)</f>
         <v>1</v>
@@ -27256,6 +27639,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D9:D10"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D31:D33"/>
@@ -27265,11 +27653,6 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="D22:D23"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
